--- a/exports/CGPOWER_full_report.xlsx
+++ b/exports/CGPOWER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.81</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44573.55208333334</v>
+        <v>44574.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>188</v>
+        <v>184.65</v>
       </c>
       <c r="I2" t="n">
         <v>184.665</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.09</v>
+        <v>-4.82</v>
       </c>
       <c r="L2" t="n">
         <v>5.05</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.44</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44642.38541666666</v>
+        <v>44642.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>171.55</v>
+        <v>174.75</v>
       </c>
       <c r="I3" t="n">
         <v>174.3848078452497</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>68</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>7.09</v>
+        <v>5.36</v>
       </c>
       <c r="L3" t="n">
         <v>3.2</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>200.1</v>
+        <v>193</v>
       </c>
       <c r="I4" t="n">
         <v>193.1009175119851</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>14.51</v>
+        <v>10.44</v>
       </c>
       <c r="L4" t="n">
         <v>1.92</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.29</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I5" t="n">
         <v>181.9942921460772</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41.83333333333334</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>7.25</v>
+        <v>5.7</v>
       </c>
       <c r="L5" t="n">
         <v>6.17</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.93</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>172.4</v>
+        <v>169.45</v>
       </c>
       <c r="I6" t="n">
         <v>170.2173495070071</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.27</v>
+        <v>-6.9</v>
       </c>
       <c r="L6" t="n">
-        <v>5.71</v>
+        <v>8.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.48</v>
+        <v>3.07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.38</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
         <v>3.12</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>7.37</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44734.55208333334</v>
+        <v>44735.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>175.65</v>
+        <v>180.7</v>
       </c>
       <c r="I7" t="n">
         <v>178.5783039665838</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.66</v>
+        <v>-6.64</v>
       </c>
       <c r="L7" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="N7" t="n">
-        <v>2.06</v>
+        <v>3.56</v>
       </c>
       <c r="O7" t="n">
         <v>-2.87</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.32</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44799.38541666666</v>
+        <v>44799.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>227.9</v>
+        <v>226.5</v>
       </c>
       <c r="I8" t="n">
         <v>226.6815432285365</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>64</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>26.12</v>
+        <v>25.35</v>
       </c>
       <c r="L8" t="n">
         <v>2.02</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6.21</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>226.8</v>
+        <v>233.2</v>
       </c>
       <c r="I9" t="n">
         <v>229.7136178032422</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.13</v>
+        <v>-2.96</v>
       </c>
       <c r="L9" t="n">
-        <v>2.14</v>
+        <v>3.53</v>
       </c>
       <c r="M9" t="n">
         <v>2.06</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44831.55208333334</v>
+        <v>44832.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>241.8</v>
+        <v>236.8</v>
       </c>
       <c r="I10" t="n">
         <v>241.5303780391973</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>3.69</v>
+        <v>1.54</v>
       </c>
       <c r="L10" t="n">
         <v>3.52</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.9</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44841.38541666666</v>
+        <v>44841.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>250.25</v>
+        <v>252.3</v>
       </c>
       <c r="I11" t="n">
         <v>251.2894963218253</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.68</v>
+        <v>-6.55</v>
       </c>
       <c r="L11" t="n">
-        <v>6.25</v>
+        <v>7.37</v>
       </c>
       <c r="M11" t="n">
         <v>0.9</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.58</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44915.38541666666</v>
+        <v>44915.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>273.85</v>
+        <v>267.95</v>
       </c>
       <c r="I12" t="n">
         <v>271.4373952829781</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>73.83333333333333</v>
+        <v>74</v>
       </c>
       <c r="K12" t="n">
-        <v>8.539999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="L12" t="n">
         <v>2.46</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.58</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44922.55208333334</v>
+        <v>44923.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>263.3</v>
+        <v>268</v>
       </c>
       <c r="I13" t="n">
         <v>267.6303322999801</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>1.74</v>
+        <v>-0.02</v>
       </c>
       <c r="L13" t="n">
         <v>2.37</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.57</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44979.38541666666</v>
+        <v>44979.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>316.45</v>
+        <v>313</v>
       </c>
       <c r="I14" t="n">
         <v>314.2836239701773</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>18.08</v>
+        <v>16.79</v>
       </c>
       <c r="L14" t="n">
         <v>2.2</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.25</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45041.38541666666</v>
+        <v>45041.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>303.85</v>
+        <v>305.6</v>
       </c>
       <c r="I15" t="n">
         <v>305.3634525927628</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>61.83333333333334</v>
+        <v>62</v>
       </c>
       <c r="K15" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="L15" t="n">
         <v>2.38</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.99</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45093.55208333334</v>
+        <v>45096.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>378.75</v>
+        <v>365.35</v>
       </c>
       <c r="I16" t="n">
         <v>366.5432686540886</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>52</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>23.94</v>
+        <v>19.55</v>
       </c>
       <c r="L16" t="n">
         <v>4.37</v>
@@ -1353,7 +1544,7 @@
         <v>0.53</v>
       </c>
       <c r="N16" t="n">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.36</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>7.38</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45112.55208333334</v>
+        <v>45113.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>384</v>
+        <v>391.45</v>
       </c>
       <c r="I17" t="n">
         <v>385.7939375603307</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.1</v>
+        <v>-7.14</v>
       </c>
       <c r="L17" t="n">
-        <v>5.38</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M17" t="n">
         <v>0.78</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.03</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45132.38541666666</v>
+        <v>45132.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>401.05</v>
+        <v>400</v>
       </c>
       <c r="I18" t="n">
         <v>400.2021406071079</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="L18" t="n">
         <v>2.95</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>5.05</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45155.55208333334</v>
+        <v>45156.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>413</v>
+        <v>427.15</v>
       </c>
       <c r="I19" t="n">
         <v>417.3585147975242</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.25</v>
+        <v>-6.79</v>
       </c>
       <c r="L19" t="n">
-        <v>6.38</v>
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
         <v>1.67</v>
       </c>
       <c r="N19" t="n">
-        <v>1.9</v>
+        <v>4.21</v>
       </c>
       <c r="O19" t="n">
         <v>-0.93</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.25</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>438.75</v>
+        <v>427.25</v>
       </c>
       <c r="I20" t="n">
         <v>428.9902981761629</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
-        <v>2.72</v>
+        <v>0.02</v>
       </c>
       <c r="L20" t="n">
         <v>5.16</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>8.57</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45251.55208333334</v>
+        <v>45252.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>389.8</v>
+        <v>469.35</v>
       </c>
       <c r="I21" t="n">
         <v>402.9320137946487</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K21" t="n">
-        <v>8.77</v>
+        <v>-9.85</v>
       </c>
       <c r="L21" t="n">
-        <v>6.42</v>
+        <v>9.85</v>
       </c>
       <c r="M21" t="n">
         <v>2.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.17</v>
+        <v>20.41</v>
       </c>
       <c r="O21" t="n">
         <v>1.88</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>18.9</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45254.55208333334</v>
+        <v>45258.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>428.4</v>
+        <v>423.15</v>
       </c>
       <c r="I22" t="n">
         <v>427.3713114195982</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.720000000000001</v>
+        <v>-9.84</v>
       </c>
       <c r="L22" t="n">
         <v>17.76</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>13.59</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45351.55208333334</v>
+        <v>45352.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>448.45</v>
+        <v>468.15</v>
       </c>
       <c r="I23" t="n">
         <v>454.4135357154546</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>93.16666666666667</v>
+        <v>94</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.98</v>
+        <v>-10.63</v>
       </c>
       <c r="L23" t="n">
-        <v>15.33</v>
+        <v>16.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>7.15</v>
       </c>
       <c r="N23" t="n">
         <v>5.05</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>7.04</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>496.45</v>
+        <v>489.9</v>
       </c>
       <c r="I24" t="n">
         <v>496.205675213388</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K24" t="n">
-        <v>6.05</v>
+        <v>4.65</v>
       </c>
       <c r="L24" t="n">
         <v>4.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.14</v>
+        <v>2.91</v>
       </c>
       <c r="N24" t="n">
         <v>4.12</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>6.01</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45398.55208333334</v>
+        <v>45400.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>517.6</v>
+        <v>529.55</v>
       </c>
       <c r="I25" t="n">
         <v>519.3496086545383</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.65</v>
+        <v>-8.09</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>8.24</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
         <v>4.99</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.57</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>687.9</v>
+        <v>612.65</v>
       </c>
       <c r="I26" t="n">
         <v>627.6722412496254</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K26" t="n">
-        <v>29.9</v>
+        <v>15.69</v>
       </c>
       <c r="L26" t="n">
         <v>3.4</v>
@@ -1923,7 +2234,7 @@
         <v>2.28</v>
       </c>
       <c r="N26" t="n">
-        <v>3.38</v>
+        <v>7.76</v>
       </c>
       <c r="O26" t="n">
         <v>2.29</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>16.25</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45464.55208333334</v>
+        <v>45467.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>678</v>
+        <v>718.15</v>
       </c>
       <c r="I27" t="n">
         <v>712.2174828753372</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>-10.67</v>
+        <v>-17.22</v>
       </c>
       <c r="L27" t="n">
-        <v>14</v>
+        <v>19.97</v>
       </c>
       <c r="M27" t="n">
         <v>2.81</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.34</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45484.55208333334</v>
+        <v>45485.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>746.85</v>
+        <v>722.55</v>
       </c>
       <c r="I28" t="n">
         <v>723.7737422664025</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>0.61</v>
       </c>
       <c r="L28" t="n">
         <v>6.47</v>
@@ -2037,7 +2372,7 @@
         <v>0.61</v>
       </c>
       <c r="N28" t="n">
-        <v>1.96</v>
+        <v>2.66</v>
       </c>
       <c r="O28" t="n">
         <v>3.98</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.16</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45497.55208333334</v>
+        <v>45498.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>699.95</v>
+        <v>733.4</v>
       </c>
       <c r="I29" t="n">
         <v>724.6781379687454</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>3.13</v>
+        <v>-1.5</v>
       </c>
       <c r="L29" t="n">
         <v>3.94</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>12.16</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>725</v>
+        <v>686.5</v>
       </c>
       <c r="I30" t="n">
         <v>688.9121069640635</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.15</v>
+        <v>-6.39</v>
       </c>
       <c r="L30" t="n">
-        <v>4.69</v>
+        <v>6.59</v>
       </c>
       <c r="M30" t="n">
-        <v>0.58</v>
+        <v>4.72</v>
       </c>
       <c r="N30" t="n">
-        <v>2.04</v>
+        <v>4.43</v>
       </c>
       <c r="O30" t="n">
         <v>3.66</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>10.56</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>710</v>
+        <v>733.35</v>
       </c>
       <c r="I31" t="n">
         <v>731.286656863994</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.42</v>
+        <v>-6.82</v>
       </c>
       <c r="L31" t="n">
-        <v>5.61</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>2.37</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>7.98</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45532.55208333334</v>
+        <v>45533.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>711.3</v>
+        <v>702.35</v>
       </c>
       <c r="I32" t="n">
         <v>707.3848500137627</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.01</v>
+        <v>-4.23</v>
       </c>
       <c r="L32" t="n">
-        <v>3.58</v>
+        <v>4.68</v>
       </c>
       <c r="M32" t="n">
         <v>0.06</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>7.69</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45546.55208333334</v>
+        <v>45547.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>693.9</v>
+        <v>737.25</v>
       </c>
       <c r="I33" t="n">
         <v>701.9823913199053</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>1.2</v>
+        <v>-4.97</v>
       </c>
       <c r="L33" t="n">
-        <v>3.05</v>
+        <v>5.08</v>
       </c>
       <c r="M33" t="n">
         <v>0.78</v>
       </c>
       <c r="N33" t="n">
-        <v>3.99</v>
+        <v>5.06</v>
       </c>
       <c r="O33" t="n">
         <v>-1.38</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.09</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>738.1</v>
+        <v>724</v>
       </c>
       <c r="I34" t="n">
         <v>737.9673788106038</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>0.12</v>
+        <v>-1.8</v>
       </c>
       <c r="L34" t="n">
         <v>6.06</v>
@@ -2379,7 +2786,7 @@
         <v>2.33</v>
       </c>
       <c r="N34" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="O34" t="n">
         <v>5.06</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>7.81</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45573.38541666666</v>
+        <v>45573.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>768.75</v>
+        <v>780.55</v>
       </c>
       <c r="I35" t="n">
         <v>771.6563002311553</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.18</v>
+        <v>-7.81</v>
       </c>
       <c r="L35" t="n">
-        <v>6.48</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>0.34</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.78</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>791</v>
+        <v>760.9</v>
       </c>
       <c r="I36" t="n">
         <v>788.5658765001334</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>1.34</v>
+        <v>-2.52</v>
       </c>
       <c r="L36" t="n">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="M36" t="n">
-        <v>0.45</v>
+        <v>1.88</v>
       </c>
       <c r="N36" t="n">
-        <v>3.13</v>
+        <v>4.3</v>
       </c>
       <c r="O36" t="n">
         <v>3.2</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>16.06</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>732.1</v>
+        <v>757.85</v>
       </c>
       <c r="I37" t="n">
         <v>741.9909832610491</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K37" t="n">
-        <v>3.78</v>
+        <v>0.4</v>
       </c>
       <c r="L37" t="n">
         <v>8.039999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.01</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>763.55</v>
+        <v>741.35</v>
       </c>
       <c r="I38" t="n">
         <v>747.4658880778862</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K38" t="n">
-        <v>0.75</v>
+        <v>-2.18</v>
       </c>
       <c r="L38" t="n">
         <v>4.24</v>
@@ -2607,7 +3062,7 @@
         <v>1.84</v>
       </c>
       <c r="N38" t="n">
-        <v>2.81</v>
+        <v>4.26</v>
       </c>
       <c r="O38" t="n">
         <v>-0.08</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>647.6</v>
+        <v>675.4</v>
       </c>
       <c r="I39" t="n">
         <v>670.4351596258063</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K39" t="n">
-        <v>12.65</v>
+        <v>8.9</v>
       </c>
       <c r="L39" t="n">
         <v>4.53</v>
@@ -2664,7 +3131,7 @@
         <v>1.22</v>
       </c>
       <c r="N39" t="n">
-        <v>4.42</v>
+        <v>5.15</v>
       </c>
       <c r="O39" t="n">
         <v>-4.26</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.87</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45681.38541666666</v>
+        <v>45681.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>622.55</v>
+        <v>620.5</v>
       </c>
       <c r="I40" t="n">
         <v>621.6267252851119</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-7.82</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="L40" t="n">
         <v>8.949999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.94</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>619.5</v>
+        <v>640.45</v>
       </c>
       <c r="I41" t="n">
         <v>637.5829494240988</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>0.16</v>
+        <v>-3.22</v>
       </c>
       <c r="L41" t="n">
-        <v>1.98</v>
+        <v>3.95</v>
       </c>
       <c r="M41" t="n">
         <v>1.3</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>13.2</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>577</v>
+        <v>556.95</v>
       </c>
       <c r="I42" t="n">
         <v>565.5025088100967</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>-9.91</v>
+        <v>-13.04</v>
       </c>
       <c r="L42" t="n">
-        <v>12.41</v>
+        <v>13.19</v>
       </c>
       <c r="M42" t="n">
         <v>0.06</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>12.66</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>603.85</v>
+        <v>613.95</v>
       </c>
       <c r="I43" t="n">
         <v>608.0215147633803</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.42</v>
+        <v>-10.23</v>
       </c>
       <c r="L43" t="n">
-        <v>9.82</v>
+        <v>10.58</v>
       </c>
       <c r="M43" t="n">
         <v>0.85</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.87</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>615.8</v>
+        <v>584.85</v>
       </c>
       <c r="I44" t="n">
         <v>611.5287902801966</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K44" t="n">
-        <v>0.3</v>
+        <v>-4.74</v>
       </c>
       <c r="L44" t="n">
         <v>5.03</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>11.73</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>598.35</v>
+        <v>615.6</v>
       </c>
       <c r="I45" t="n">
         <v>601.643480776801</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.31</v>
+        <v>-5.26</v>
       </c>
       <c r="L45" t="n">
-        <v>5.86</v>
+        <v>6.15</v>
       </c>
       <c r="M45" t="n">
         <v>3.04</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.15</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>632.15</v>
+        <v>596</v>
       </c>
       <c r="I46" t="n">
         <v>614.1341191111661</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>2.69</v>
+        <v>-3.18</v>
       </c>
       <c r="L46" t="n">
-        <v>3.16</v>
+        <v>5.21</v>
       </c>
       <c r="M46" t="n">
         <v>0.5600000000000001</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>11.63</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>651.4</v>
+        <v>669.65</v>
       </c>
       <c r="I47" t="n">
         <v>659.9617640035091</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-9.300000000000001</v>
+        <v>-12.36</v>
       </c>
       <c r="L47" t="n">
-        <v>10.3</v>
+        <v>13.08</v>
       </c>
       <c r="M47" t="n">
         <v>3.27</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.08</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45863.38541666666</v>
+        <v>45863.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>668.9</v>
+        <v>661.6</v>
       </c>
       <c r="I48" t="n">
         <v>664.2490102485127</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>72</v>
+        <v>72.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.11</v>
+        <v>-1.2</v>
       </c>
       <c r="L48" t="n">
         <v>3.23</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.8</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45897.55208333334</v>
+        <v>45898.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>663.5</v>
+        <v>695.7</v>
       </c>
       <c r="I49" t="n">
         <v>687.5562253961882</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.29</v>
+        <v>-5.15</v>
       </c>
       <c r="L49" t="n">
-        <v>3.93</v>
+        <v>5.77</v>
       </c>
       <c r="M49" t="n">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="N49" t="n">
-        <v>2.43</v>
+        <v>4.74</v>
       </c>
       <c r="O49" t="n">
         <v>-2.99</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>768.5</v>
+        <v>760.1</v>
       </c>
       <c r="I50" t="n">
         <v>760.4913770380675</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>10.46</v>
+        <v>9.26</v>
       </c>
       <c r="L50" t="n">
         <v>3.95</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.38</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45959.38541666666</v>
+        <v>45959.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>730.35</v>
+        <v>753.4</v>
       </c>
       <c r="I51" t="n">
         <v>752.4524877167029</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K51" t="n">
-        <v>3.91</v>
+        <v>0.88</v>
       </c>
       <c r="L51" t="n">
         <v>1.11</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>6.84</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45979.55208333334</v>
+        <v>45980.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>732.95</v>
+        <v>719.85</v>
       </c>
       <c r="I52" t="n">
         <v>720.0472827305058</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.71</v>
+        <v>-4.45</v>
       </c>
       <c r="L52" t="n">
-        <v>4.43</v>
+        <v>4.51</v>
       </c>
       <c r="M52" t="n">
         <v>0.8</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.22</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46050.55208333334</v>
+        <v>46051.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>581.95</v>
+        <v>585</v>
       </c>
       <c r="I53" t="n">
         <v>584.482432405075</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>70.16666666666667</v>
+        <v>71</v>
       </c>
       <c r="K53" t="n">
-        <v>19.16</v>
+        <v>18.73</v>
       </c>
       <c r="L53" t="n">
         <v>1.97</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>713</v>
+        <v>682.75</v>
       </c>
       <c r="I54" t="n">
         <v>691.9328352404729</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K54" t="n">
-        <v>21.88</v>
+        <v>16.71</v>
       </c>
       <c r="L54" t="n">
         <v>6.25</v>
@@ -3519,7 +4166,7 @@
         <v>4.93</v>
       </c>
       <c r="N54" t="n">
-        <v>2.01</v>
+        <v>3.88</v>
       </c>
       <c r="O54" t="n">
         <v>1.42</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.1</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46091.38541666666</v>
+        <v>46091.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>725.55</v>
+        <v>730</v>
       </c>
       <c r="I55" t="n">
         <v>727.9913792987257</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.27</v>
+        <v>-6.92</v>
       </c>
       <c r="L55" t="n">
-        <v>6.74</v>
+        <v>7.21</v>
       </c>
       <c r="M55" t="n">
         <v>1.44</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>7.21</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46101.38541666666</v>
+        <v>46101.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>687.2</v>
+        <v>681</v>
       </c>
       <c r="I56" t="n">
         <v>683.9299792250782</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.86</v>
+        <v>-6.71</v>
       </c>
       <c r="L56" t="n">
-        <v>6.84</v>
+        <v>7.03</v>
       </c>
       <c r="M56" t="n">
         <v>1.4</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.66</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>693.95</v>
+        <v>729</v>
       </c>
       <c r="I57" t="n">
         <v>707.6181651579283</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.9</v>
+        <v>-7.05</v>
       </c>
       <c r="L57" t="n">
-        <v>2.03</v>
+        <v>7.28</v>
       </c>
       <c r="M57" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="N57" t="n">
-        <v>3.74</v>
+        <v>4.62</v>
       </c>
       <c r="O57" t="n">
         <v>-1.16</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.26</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46160.38541666666</v>
+        <v>46160.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>811.85</v>
+        <v>808.65</v>
       </c>
       <c r="I58" t="n">
         <v>809.4840774029035</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>11.36</v>
+        <v>10.93</v>
       </c>
       <c r="L58" t="n">
         <v>3.26</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>6.79</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46162.55208333334</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>856.4</v>
+        <v>865.9</v>
       </c>
       <c r="I59" t="n">
         <v>863.551202704283</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.9</v>
+        <v>-7.08</v>
       </c>
       <c r="L59" t="n">
-        <v>6.07</v>
+        <v>7.34</v>
       </c>
       <c r="M59" t="n">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
         <v>4.5</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.82</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>957.4</v>
+        <v>892.6</v>
       </c>
       <c r="I60" t="n">
         <v>915.5531078188096</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K60" t="n">
-        <v>10.57</v>
+        <v>3.08</v>
       </c>
       <c r="L60" t="n">
         <v>1.02</v>
       </c>
       <c r="M60" t="n">
-        <v>1.93</v>
+        <v>4.8</v>
       </c>
       <c r="N60" t="n">
-        <v>4.29</v>
+        <v>6.58</v>
       </c>
       <c r="O60" t="n">
         <v>0.9</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.35</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46238.38541666666</v>
+        <v>46238.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>875.8</v>
+        <v>881.35</v>
       </c>
       <c r="I61" t="n">
         <v>879.2106595292881</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K61" t="n">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="L61" t="n">
         <v>6.98</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.71</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46253.38541666666</v>
+        <v>46253.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>870</v>
+        <v>861.55</v>
       </c>
       <c r="I62" t="n">
         <v>865.181165926582</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.29</v>
+        <v>-2.25</v>
       </c>
       <c r="L62" t="n">
         <v>2.4</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>4.67</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46269.55208333334</v>
+        <v>46272.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>894.6</v>
+        <v>900.6</v>
       </c>
       <c r="I63" t="n">
         <v>897.8529937425751</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.84</v>
+        <v>-4.53</v>
       </c>
       <c r="L63" t="n">
-        <v>4.87</v>
+        <v>5.86</v>
       </c>
       <c r="M63" t="n">
         <v>1.25</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>3.83</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>912.5</v>
+        <v>874.25</v>
       </c>
       <c r="I64" t="n">
         <v>890.8969576910886</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K64" t="n">
-        <v>1.32</v>
+        <v>-2.93</v>
       </c>
       <c r="L64" t="n">
-        <v>1.29</v>
+        <v>3.59</v>
       </c>
       <c r="M64" t="n">
         <v>0.57</v>
       </c>
       <c r="N64" t="n">
-        <v>1.87</v>
+        <v>5.86</v>
       </c>
       <c r="O64" t="n">
         <v>0.6</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.29</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>880.5</v>
+        <v>907.7</v>
       </c>
       <c r="I65" t="n">
         <v>902.9752023644212</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.71</v>
+        <v>-3.83</v>
       </c>
       <c r="L65" t="n">
         <v>4.24</v>
@@ -4146,7 +4925,7 @@
         <v>0.54</v>
       </c>
       <c r="N65" t="n">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="O65" t="n">
         <v>-5.86</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.14</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46293.38541666666</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="I66" t="n">
         <v>865.5948054532523</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.04</v>
+        <v>-4.81</v>
       </c>
       <c r="L66" t="n">
-        <v>4.23</v>
+        <v>4.89</v>
       </c>
       <c r="M66" t="n">
         <v>2</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>5.52</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>882.3</v>
+        <v>908.95</v>
       </c>
       <c r="I67" t="n">
         <v>903.0241993719659</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.12</v>
+        <v>-5.2</v>
       </c>
       <c r="L67" t="n">
-        <v>3.5</v>
+        <v>5.71</v>
       </c>
       <c r="M67" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N67" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="O67" t="n">
         <v>-2.49</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>6.46</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46303.38541666666</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>870.05</v>
+        <v>862.8</v>
       </c>
       <c r="I68" t="n">
         <v>863.165176286563</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.28</v>
+        <v>-5.08</v>
       </c>
       <c r="L68" t="n">
-        <v>4.58</v>
+        <v>5.17</v>
       </c>
       <c r="M68" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="N68" t="n">
         <v>3.37</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>25</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.9</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>93.2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62.7</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7372,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7382,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7392,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70.09999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.89</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.22</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.52</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.9</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.7</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.09</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.43</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7472,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.76</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7492,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7512,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.93</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.73</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7532,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.69</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
